--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484694_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484694_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.0138</v>
+        <v>1.9205</v>
       </c>
       <c r="E2" t="n">
-        <v>2.3687</v>
+        <v>2.1764</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.355</v>
+        <v>-0.2559</v>
       </c>
       <c r="G2" t="n">
         <v>1.2704</v>
@@ -610,13 +610,13 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6151</v>
+        <v>0.5219</v>
       </c>
       <c r="T2" t="n">
-        <v>0.494</v>
+        <v>0.3017</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1211</v>
+        <v>0.2202</v>
       </c>
       <c r="V2" t="n">
         <v>0.3115</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.332</v>
+        <v>0.4252</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.442</v>
+        <v>-1.2496</v>
       </c>
       <c r="F4" t="n">
-        <v>1.774</v>
+        <v>1.6749</v>
       </c>
       <c r="G4" t="n">
         <v>1.0021</v>
@@ -766,13 +766,13 @@
         <v>1.0995</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8534</v>
+        <v>-0.7602</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7526</v>
+        <v>-0.5603</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1008</v>
+        <v>-0.1999</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.131</v>
+        <v>0.186</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.9747</v>
+        <v>-0.9196</v>
       </c>
       <c r="F5" t="n">
         <v>1.1057</v>
@@ -844,10 +844,10 @@
         <v>2.0158</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3296</v>
+        <v>-0.2745</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4057</v>
+        <v>-0.3506</v>
       </c>
       <c r="U5" t="n">
         <v>0.0761</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3337</v>
+        <v>-0.251</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.2801</v>
+        <v>-1.3212</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9464</v>
+        <v>1.0703</v>
       </c>
       <c r="G6" t="n">
         <v>-1.2045</v>
@@ -922,13 +922,13 @@
         <v>2.0158</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3571</v>
+        <v>-0.2743</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2405</v>
+        <v>-0.2816</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1165</v>
+        <v>0.0073</v>
       </c>
       <c r="V6" t="n">
         <v>0.3115</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5323</v>
+        <v>-0.3648</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.3308</v>
+        <v>-3.1385</v>
       </c>
       <c r="F7" t="n">
-        <v>2.7985</v>
+        <v>2.7737</v>
       </c>
       <c r="G7" t="n">
         <v>0.6124000000000001</v>
@@ -1000,13 +1000,13 @@
         <v>1.0995</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0897</v>
+        <v>0.0779</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4042</v>
+        <v>-0.2119</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3145</v>
+        <v>0.2898</v>
       </c>
       <c r="V7" t="n">
         <v>-0.3219</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. MELGAR GARCIA</t>
+          <t>D. BORISOV</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9466</v>
+        <v>-1.3042</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7358</v>
+        <v>0.5422</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7892</v>
+        <v>-1.8464</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.5743</v>
+        <v>4.541</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.1575</v>
+        <v>0.4474</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4167</v>
+        <v>4.0936</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.174</v>
+        <v>4.6499</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.5329</v>
+        <v>0.7803</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.641</v>
+        <v>3.8696</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5997</v>
+        <v>-0.1089</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3754</v>
+        <v>-0.3329</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2243</v>
+        <v>0.224</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5498</v>
+        <v>-1.4661</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.1833</v>
+        <v>-3.8484</v>
       </c>
       <c r="R8" t="n">
-        <v>0.733</v>
+        <v>2.3823</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0779</v>
+        <v>-0.9106</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6214</v>
+        <v>-0.9136</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5435</v>
+        <v>0.003</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-3.4686</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.6543</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-4.1229</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. BORISOV</t>
+          <t>A. MELGAR GARCIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1582</v>
+        <v>-1.3501</v>
       </c>
       <c r="E9" t="n">
-        <v>0.391</v>
+        <v>-2.3127</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.5492</v>
+        <v>0.9626</v>
       </c>
       <c r="G9" t="n">
-        <v>4.541</v>
+        <v>-1.5743</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4474</v>
+        <v>-1.1575</v>
       </c>
       <c r="I9" t="n">
-        <v>4.0936</v>
+        <v>-0.4167</v>
       </c>
       <c r="J9" t="n">
-        <v>4.6499</v>
+        <v>-2.174</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7803</v>
+        <v>-1.5329</v>
       </c>
       <c r="L9" t="n">
-        <v>3.8696</v>
+        <v>-0.641</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1089</v>
+        <v>0.5997</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3329</v>
+        <v>0.3754</v>
       </c>
       <c r="O9" t="n">
-        <v>0.224</v>
+        <v>0.2243</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.4661</v>
+        <v>0.5498</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.8484</v>
+        <v>-0.1833</v>
       </c>
       <c r="R9" t="n">
-        <v>2.3823</v>
+        <v>0.733</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7645999999999999</v>
+        <v>-0.3256</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0648</v>
+        <v>0.0445</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3003</v>
+        <v>-0.3701</v>
       </c>
       <c r="V9" t="n">
-        <v>-3.4686</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6543</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-4.1229</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7437</v>
+        <v>-1.6228</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.0756</v>
+        <v>-2.9795</v>
       </c>
       <c r="F10" t="n">
-        <v>1.3319</v>
+        <v>1.3567</v>
       </c>
       <c r="G10" t="n">
         <v>-0.4329</v>
@@ -1234,13 +1234,13 @@
         <v>1.0995</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8998</v>
+        <v>-0.7788</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6606</v>
+        <v>-0.5645</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2392</v>
+        <v>-0.2144</v>
       </c>
       <c r="V10" t="n">
         <v>0.3219</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.5692</v>
+        <v>-3.3437</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.0922</v>
+        <v>-4.941</v>
       </c>
       <c r="F11" t="n">
-        <v>1.523</v>
+        <v>1.5974</v>
       </c>
       <c r="G11" t="n">
         <v>-2.7755</v>
@@ -1312,13 +1312,13 @@
         <v>3.1154</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8486</v>
+        <v>-0.6231</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7541</v>
+        <v>-0.6029</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0945</v>
+        <v>-0.0202</v>
       </c>
       <c r="V11" t="n">
         <v>-0.3115</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.4656</v>
+        <v>-5.2926</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.5991</v>
+        <v>-3.3518</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.8665</v>
+        <v>-1.9408</v>
       </c>
       <c r="G12" t="n">
         <v>-2.7939</v>
@@ -1390,13 +1390,13 @@
         <v>2.0158</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6717</v>
+        <v>-0.4987</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6976</v>
+        <v>-0.4502</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0258</v>
+        <v>-0.0485</v>
       </c>
       <c r="V12" t="n">
         <v>-1.267</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-10.3223</v>
+        <v>-10.0473</v>
       </c>
       <c r="E13" t="n">
-        <v>-16.8204</v>
+        <v>-16.5451</v>
       </c>
       <c r="F13" t="n">
-        <v>6.498000000000001</v>
+        <v>6.4982</v>
       </c>
       <c r="G13" t="n">
         <v>1.594900000000001</v>
@@ -1468,10 +1468,10 @@
         <v>15.5766</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.121499999999999</v>
+        <v>-3.846</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.8647</v>
+        <v>-3.5894</v>
       </c>
       <c r="U13" t="n">
         <v>-0.2567</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>K. MONTANO LINARES</t>
+          <t>M. PANOS HUERTAS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.3209</v>
+        <v>5.8508</v>
       </c>
       <c r="E14" t="n">
-        <v>2.456</v>
+        <v>3.586</v>
       </c>
       <c r="F14" t="n">
-        <v>2.8649</v>
+        <v>2.2648</v>
       </c>
       <c r="G14" t="n">
-        <v>2.206</v>
+        <v>1.5178</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3145</v>
+        <v>1.1682</v>
       </c>
       <c r="I14" t="n">
-        <v>1.8916</v>
+        <v>0.3496</v>
       </c>
       <c r="J14" t="n">
-        <v>2.2736</v>
+        <v>1.2968</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2535</v>
+        <v>1.2354</v>
       </c>
       <c r="L14" t="n">
-        <v>2.0201</v>
+        <v>0.0614</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.06759999999999999</v>
+        <v>0.221</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0609</v>
+        <v>-0.0673</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1285</v>
+        <v>0.2882</v>
       </c>
       <c r="P14" t="n">
+        <v>1.8326</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-0.1833</v>
+      </c>
+      <c r="R14" t="n">
         <v>2.0158</v>
       </c>
-      <c r="Q14" t="n">
-        <v>-1.2828</v>
-      </c>
-      <c r="R14" t="n">
-        <v>3.2986</v>
-      </c>
       <c r="S14" t="n">
-        <v>0.9038</v>
+        <v>0.2885</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8213</v>
+        <v>-0.0614</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0825</v>
+        <v>0.3499</v>
       </c>
       <c r="V14" t="n">
-        <v>0.1953</v>
+        <v>2.212</v>
       </c>
       <c r="W14" t="n">
-        <v>0.6439</v>
+        <v>2.5339</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.4486</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. PANOS HUERTAS</t>
+          <t>P. ROCATI ALEGRE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,40 +1579,40 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.5249</v>
+        <v>5.3294</v>
       </c>
       <c r="E15" t="n">
-        <v>2.913</v>
+        <v>0.5946</v>
       </c>
       <c r="F15" t="n">
-        <v>1.612</v>
+        <v>4.7348</v>
       </c>
       <c r="G15" t="n">
-        <v>1.5178</v>
+        <v>-1.284</v>
       </c>
       <c r="H15" t="n">
-        <v>1.1682</v>
+        <v>-0.1172</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3496</v>
+        <v>-1.1669</v>
       </c>
       <c r="J15" t="n">
-        <v>1.2968</v>
+        <v>-2.3323</v>
       </c>
       <c r="K15" t="n">
-        <v>1.2354</v>
+        <v>-1.1336</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0614</v>
+        <v>-1.1987</v>
       </c>
       <c r="M15" t="n">
-        <v>0.221</v>
+        <v>1.0483</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0673</v>
+        <v>1.0164</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2882</v>
+        <v>0.0318</v>
       </c>
       <c r="P15" t="n">
         <v>1.8326</v>
@@ -1624,28 +1624,28 @@
         <v>2.0158</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0374</v>
+        <v>0.494</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7345</v>
+        <v>-0.0573</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3029</v>
+        <v>0.5513</v>
       </c>
       <c r="V15" t="n">
-        <v>2.212</v>
+        <v>4.2869</v>
       </c>
       <c r="W15" t="n">
-        <v>2.5339</v>
+        <v>3.1674</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.3219</v>
+        <v>1.1195</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. ROCATI ALEGRE</t>
+          <t>K. MONTANO LINARES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.0356</v>
+        <v>5.0849</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1747</v>
+        <v>1.6868</v>
       </c>
       <c r="F16" t="n">
-        <v>4.2102</v>
+        <v>3.3982</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.284</v>
+        <v>2.206</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1172</v>
+        <v>0.3145</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.1669</v>
+        <v>1.8916</v>
       </c>
       <c r="J16" t="n">
-        <v>-2.3323</v>
+        <v>2.2736</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.1336</v>
+        <v>0.2535</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.1987</v>
+        <v>2.0201</v>
       </c>
       <c r="M16" t="n">
-        <v>1.0483</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>1.0164</v>
+        <v>0.0609</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0318</v>
+        <v>-0.1285</v>
       </c>
       <c r="P16" t="n">
-        <v>1.8326</v>
+        <v>2.0158</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.1833</v>
+        <v>-1.2828</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0158</v>
+        <v>3.2986</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7998</v>
+        <v>0.6677999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8265</v>
+        <v>0.0521</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0267</v>
+        <v>0.6157</v>
       </c>
       <c r="V16" t="n">
-        <v>4.2869</v>
+        <v>0.1953</v>
       </c>
       <c r="W16" t="n">
-        <v>3.1674</v>
+        <v>0.6439</v>
       </c>
       <c r="X16" t="n">
-        <v>1.1195</v>
+        <v>-0.4486</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. AZNAR MARTINEZ</t>
+          <t>A. MARTIN MARGARIT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.7518</v>
+        <v>1.5091</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0649</v>
+        <v>-1.247</v>
       </c>
       <c r="F17" t="n">
-        <v>1.8168</v>
+        <v>2.7561</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.8608</v>
+        <v>1.0667</v>
       </c>
       <c r="H17" t="n">
-        <v>1.1395</v>
+        <v>0.7079</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.0004</v>
+        <v>0.3589</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.6818</v>
+        <v>1.0212</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5169</v>
+        <v>0.8545</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.1987</v>
+        <v>0.1667</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.179</v>
+        <v>0.0456</v>
       </c>
       <c r="N17" t="n">
-        <v>0.6226</v>
+        <v>-0.1466</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.8017</v>
+        <v>0.1922</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.0158</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.8484</v>
+        <v>-2.1991</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8326</v>
+        <v>2.1991</v>
       </c>
       <c r="S17" t="n">
-        <v>3.3615</v>
+        <v>0.5586</v>
       </c>
       <c r="T17" t="n">
-        <v>1.6094</v>
+        <v>-0.0795</v>
       </c>
       <c r="U17" t="n">
-        <v>1.7521</v>
+        <v>0.6382</v>
       </c>
       <c r="V17" t="n">
-        <v>1.267</v>
+        <v>-0.1163</v>
       </c>
       <c r="W17" t="n">
-        <v>2.8559</v>
+        <v>0.0104</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.5889</v>
+        <v>-0.1267</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. MARTIN MARGARIT</t>
+          <t>J. BALLESTER FERRANDIS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.4727</v>
+        <v>0.984</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.1509</v>
+        <v>-1.5332</v>
       </c>
       <c r="F18" t="n">
-        <v>2.6236</v>
+        <v>2.5172</v>
       </c>
       <c r="G18" t="n">
-        <v>1.0667</v>
+        <v>-1.0164</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7079</v>
+        <v>0.522</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3589</v>
+        <v>-1.5385</v>
       </c>
       <c r="J18" t="n">
-        <v>1.0212</v>
+        <v>-2.7625</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8545</v>
+        <v>-0.1983</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1667</v>
+        <v>-2.5641</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0456</v>
+        <v>1.746</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1466</v>
+        <v>0.7204</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1922</v>
+        <v>1.0256</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.9163</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.1991</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.1991</v>
+        <v>0.9163</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5222</v>
+        <v>0.2658</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0166</v>
+        <v>-0.0377</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5056</v>
+        <v>0.3035</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.1163</v>
+        <v>0.8183</v>
       </c>
       <c r="W18" t="n">
-        <v>0.0104</v>
+        <v>1.267</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1267</v>
+        <v>-0.4486</v>
       </c>
     </row>
     <row r="19">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3925</v>
+        <v>0.2031</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1184</v>
+        <v>-0.4069</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5109</v>
+        <v>0.61</v>
       </c>
       <c r="G20" t="n">
         <v>-0.3291</v>
@@ -2014,13 +2014,13 @@
         <v>1.2828</v>
       </c>
       <c r="S20" t="n">
-        <v>1.1649</v>
+        <v>0.9755</v>
       </c>
       <c r="T20" t="n">
-        <v>0.6576</v>
+        <v>0.3692</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5072</v>
+        <v>0.6063</v>
       </c>
       <c r="V20" t="n">
         <v>-1.726</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. BALLESTER FERRANDIS</t>
+          <t>A. AZNAR MARTINEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3517</v>
+        <v>0.0121</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.9178</v>
+        <v>-1.2188</v>
       </c>
       <c r="F21" t="n">
-        <v>2.2694</v>
+        <v>1.2309</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.0164</v>
+        <v>-0.8608</v>
       </c>
       <c r="H21" t="n">
-        <v>0.522</v>
+        <v>1.1395</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.5385</v>
+        <v>-2.0004</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.7625</v>
+        <v>-0.6818</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.1983</v>
+        <v>0.5169</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.5641</v>
+        <v>-1.1987</v>
       </c>
       <c r="M21" t="n">
-        <v>1.746</v>
+        <v>-0.179</v>
       </c>
       <c r="N21" t="n">
-        <v>0.7204</v>
+        <v>0.6226</v>
       </c>
       <c r="O21" t="n">
-        <v>1.0256</v>
+        <v>-0.8017</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9163</v>
+        <v>-2.0158</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-3.8484</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9163</v>
+        <v>1.8326</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3665</v>
+        <v>1.6218</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4223</v>
+        <v>0.4555</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0558</v>
+        <v>1.1663</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8183</v>
+        <v>1.267</v>
       </c>
       <c r="W21" t="n">
-        <v>1.267</v>
+        <v>2.8559</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.4486</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. MATE SEBASTIA</t>
+          <t>B. MONDRAGON VIDAL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.7521</v>
+        <v>-3.4951</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.0784</v>
+        <v>-4.9312</v>
       </c>
       <c r="F22" t="n">
-        <v>1.3263</v>
+        <v>1.4361</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.0953</v>
+        <v>-2.7752</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.2585</v>
+        <v>-0.3071</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1632</v>
+        <v>-2.468</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.4035</v>
+        <v>-1.2331</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.1119</v>
+        <v>-0.1116</v>
       </c>
       <c r="L22" t="n">
-        <v>0.7085</v>
+        <v>-1.1214</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.6919</v>
+        <v>-1.5421</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1466</v>
+        <v>-0.1955</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.5452</v>
+        <v>-1.3466</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.7489</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.7647</v>
+        <v>-3.1154</v>
       </c>
       <c r="R22" t="n">
-        <v>2.0158</v>
+        <v>2.7489</v>
       </c>
       <c r="S22" t="n">
-        <v>1.359</v>
+        <v>0.2696</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0898</v>
+        <v>-0.2816</v>
       </c>
       <c r="U22" t="n">
-        <v>1.2693</v>
+        <v>0.5513</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.267</v>
+        <v>-0.6231</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.3011</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.267</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B. MONDRAGON VIDAL</t>
+          <t>J. MATE SEBASTIA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.751</v>
+        <v>-4.2083</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.6043</v>
+        <v>-5.2707</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8532999999999999</v>
+        <v>1.0624</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.7752</v>
+        <v>-1.0953</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.3071</v>
+        <v>-1.2585</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.468</v>
+        <v>0.1632</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.2331</v>
+        <v>-0.4035</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.1116</v>
+        <v>-1.1119</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.1214</v>
+        <v>0.7085</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.5421</v>
+        <v>-0.6919</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.1955</v>
+        <v>-0.1466</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.3466</v>
+        <v>-0.5452</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.3665</v>
+        <v>-2.7489</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.1154</v>
+        <v>-4.7647</v>
       </c>
       <c r="R23" t="n">
-        <v>2.7489</v>
+        <v>2.0158</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9863</v>
+        <v>0.9029</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9547</v>
+        <v>-0.1025</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0315</v>
+        <v>1.0054</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.6231</v>
+        <v>-1.267</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.3011</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.3219</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>10.3223</v>
+        <v>12.2453</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.765100000000001</v>
+        <v>-7.765099999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>18.0874</v>
+        <v>20.0105</v>
       </c>
       <c r="G24" t="n">
         <v>-1.595</v>
@@ -2299,10 +2299,10 @@
         <v>-4.0068</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.255800000000001</v>
+        <v>-3.2558</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.2126999999999995</v>
+        <v>-0.2127</v>
       </c>
       <c r="L24" t="n">
         <v>-3.0429</v>
@@ -2326,22 +2326,22 @@
         <v>18.3257</v>
       </c>
       <c r="S24" t="n">
-        <v>4.1214</v>
+        <v>6.044499999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2567</v>
+        <v>0.2568</v>
       </c>
       <c r="U24" t="n">
-        <v>3.8648</v>
+        <v>5.7879</v>
       </c>
       <c r="V24" t="n">
-        <v>5.047100000000001</v>
+        <v>5.0471</v>
       </c>
       <c r="W24" t="n">
         <v>10.8109</v>
       </c>
       <c r="X24" t="n">
-        <v>-5.763599999999999</v>
+        <v>-5.7636</v>
       </c>
     </row>
   </sheetData>
